--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP156" headerRowCount="1">
-  <autoFilter ref="A1:EP156"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP157" headerRowCount="1">
+  <autoFilter ref="A1:EP157"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP156"/>
+  <dimension ref="A1:EP157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE3" t="n">
         <v>2</v>
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE8" t="n">
         <v>1.82</v>
@@ -8421,7 +8421,7 @@
         <v>2.12</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>1.17</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>1.5</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -11314,7 +11314,7 @@
         <v>50</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE22" t="n">
         <v>0.82</v>
@@ -15601,7 +15601,7 @@
         <v>1</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF31" t="n">
         <v>1.33</v>
@@ -17518,7 +17518,7 @@
         <v>67</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE35" t="n">
         <v>2.18</v>
@@ -19425,7 +19425,7 @@
         <v>1.71</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF39" t="n">
         <v>1</v>
@@ -19886,7 +19886,7 @@
         <v>63</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE40" t="n">
         <v>1.5</v>
@@ -22750,7 +22750,7 @@
         <v>70</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE46" t="n">
         <v>1.18</v>
@@ -24177,7 +24177,7 @@
         <v>0.76</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF49" t="n">
         <v>1.2</v>
@@ -27022,7 +27022,7 @@
         <v>67</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE55" t="n">
         <v>0.82</v>
@@ -29873,7 +29873,7 @@
         <v>2</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF61" t="n">
         <v>2.33</v>
@@ -31305,7 +31305,7 @@
         <v>1</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF64" t="n">
         <v>0.71</v>
@@ -32270,7 +32270,7 @@
         <v>57</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE66" t="n">
         <v>2.06</v>
@@ -36529,7 +36529,7 @@
         <v>2.06</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF75" t="n">
         <v>2.5</v>
@@ -37974,7 +37974,7 @@
         <v>82</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE78" t="n">
         <v>1.18</v>
@@ -40377,7 +40377,7 @@
         <v>0.71</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF83" t="n">
         <v>0.44</v>
@@ -41310,7 +41310,7 @@
         <v>67</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE85" t="n">
         <v>1.17</v>
@@ -44630,7 +44630,7 @@
         <v>70</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE92" t="n">
         <v>0.76</v>
@@ -46038,7 +46038,7 @@
         <v>70</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE95" t="n">
         <v>0.9399999999999999</v>
@@ -48873,7 +48873,7 @@
         <v>1</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF101" t="n">
         <v>0.82</v>
@@ -49833,7 +49833,7 @@
         <v>1</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF103" t="n">
         <v>0.91</v>
@@ -54566,10 +54566,10 @@
         <v>79</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF113" t="n">
         <v>1.5</v>
@@ -54599,7 +54599,7 @@
         <v>2.83</v>
       </c>
       <c r="DO113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -58777,7 +58777,7 @@
         <v>1.82</v>
       </c>
       <c r="DE122" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF122" t="n">
         <v>2.08</v>
@@ -59242,7 +59242,7 @@
         <v>66</v>
       </c>
       <c r="DD123" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE123" t="n">
         <v>2.12</v>
@@ -61642,7 +61642,7 @@
         <v>79</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE128" t="n">
         <v>0.71</v>
@@ -65449,7 +65449,7 @@
         <v>2.18</v>
       </c>
       <c r="DE136" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF136" t="n">
         <v>2.29</v>
@@ -66385,7 +66385,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DE138" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF138" t="n">
         <v>1.07</v>
@@ -69718,7 +69718,7 @@
         <v>73</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE145" t="n">
         <v>1.71</v>
@@ -70190,7 +70190,7 @@
         <v>88</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DE146" t="n">
         <v>1.18</v>
@@ -73989,7 +73989,7 @@
         <v>1.18</v>
       </c>
       <c r="DE154" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DF154" t="n">
         <v>1.06</v>
@@ -74458,7 +74458,7 @@
         <v>62</v>
       </c>
       <c r="DD155" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DE155" t="n">
         <v>1.17</v>
@@ -74949,7 +74949,7 @@
         <v>1.5</v>
       </c>
       <c r="DE156" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DF156" t="n">
         <v>1.41</v>
@@ -75096,6 +75096,494 @@
       <c r="EP156" t="inlineStr">
         <is>
           <t>2.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Mexico_Liga_MX_2025-2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Juárez</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>45985.04166666666</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>2</v>
+      </c>
+      <c r="L157" t="n">
+        <v>2</v>
+      </c>
+      <c r="M157" t="n">
+        <v>4</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>1</v>
+      </c>
+      <c r="P157" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>5</v>
+      </c>
+      <c r="R157" t="n">
+        <v>4</v>
+      </c>
+      <c r="S157" t="n">
+        <v>4</v>
+      </c>
+      <c r="T157" t="n">
+        <v>6</v>
+      </c>
+      <c r="U157" t="n">
+        <v>9</v>
+      </c>
+      <c r="V157" t="n">
+        <v>10</v>
+      </c>
+      <c r="W157" t="n">
+        <v>9</v>
+      </c>
+      <c r="X157" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Estadio Olímpico Benito Juárez</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>Avenida Heroico Colegio Militar, Ciudad Juárez</t>
+        </is>
+      </c>
+      <c r="AC157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>1444</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV157" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW157" t="n">
+        <v>19</v>
+      </c>
+      <c r="BX157" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY157" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ157" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA157" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB157" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP157" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR157" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS157" t="n">
+        <v>39</v>
+      </c>
+      <c r="CT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU157" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV157" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW157" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX157" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY157" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ157" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA157" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB157" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC157" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD157" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DE157" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DF157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DG157" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DH157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DI157" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DJ157" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK157" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL157" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM157" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN157" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DO157" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU157" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV157" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW157" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="DX157" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="DY157" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="DZ157" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA157" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EB157" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EC157" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="ED157" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EE157" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EF157" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EG157" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EH157" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="EI157" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ157" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EK157" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL157" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EM157" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EN157" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EO157" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EP157" t="inlineStr">
+        <is>
+          <t>2.42</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -78966,13 +78966,13 @@
         <v>6</v>
       </c>
       <c r="T165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U165" t="n">
         <v>9</v>
       </c>
       <c r="V165" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W165" t="n">
         <v>11</v>
@@ -78988,12 +78988,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>Estadio Azteca</t>
+          <t>Estadio Olímpico de Universitario</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan 3665, Coyoacán, D.F.</t>
+          <t>Calle Escobar, Colonia Ciudad Universitaria, Coyoacán, D.F.</t>
         </is>
       </c>
       <c r="AC165" t="n">
@@ -79147,10 +79147,10 @@
         <v>1.03</v>
       </c>
       <c r="CA165" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="CB165" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="CC165" t="n">
         <v>0</v>
@@ -79201,7 +79201,7 @@
         <v>14</v>
       </c>
       <c r="CS165" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CT165" t="n">
         <v>1</v>
@@ -79216,7 +79216,7 @@
         <v>1</v>
       </c>
       <c r="CX165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CY165" t="n">
         <v>7</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -80429,10 +80429,10 @@
         <v>7</v>
       </c>
       <c r="Y168" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z168" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -80649,7 +80649,7 @@
         <v>22</v>
       </c>
       <c r="CS168" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CT168" t="n">
         <v>1</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -81382,13 +81382,13 @@
         <v>8</v>
       </c>
       <c r="T170" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U170" t="n">
         <v>10</v>
       </c>
       <c r="V170" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W170" t="n">
         <v>14</v>
@@ -81563,10 +81563,10 @@
         <v>1.06</v>
       </c>
       <c r="CA170" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="CB170" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="CC170" t="n">
         <v>0</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP170" headerRowCount="1">
-  <autoFilter ref="A1:EP170"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP171" headerRowCount="1">
+  <autoFilter ref="A1:EP171"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP170"/>
+  <dimension ref="A1:EP171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE6" t="n">
         <v>1</v>
@@ -6029,7 +6029,7 @@
         <v>1.18</v>
       </c>
       <c r="DE11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -7938,7 +7938,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE15" t="n">
         <v>1.29</v>
@@ -13206,10 +13206,10 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE26" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13239,7 +13239,7 @@
         <v>4.42</v>
       </c>
       <c r="DO26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14166,7 +14166,7 @@
         <v>59</v>
       </c>
       <c r="DD28" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE28" t="n">
         <v>0.71</v>
@@ -17521,7 +17521,7 @@
         <v>1.29</v>
       </c>
       <c r="DE35" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF35" t="n">
         <v>0.67</v>
@@ -20358,7 +20358,7 @@
         <v>84</v>
       </c>
       <c r="DD41" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE41" t="n">
         <v>1.95</v>
@@ -21318,7 +21318,7 @@
         <v>88</v>
       </c>
       <c r="DD43" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE43" t="n">
         <v>1.17</v>
@@ -24657,7 +24657,7 @@
         <v>0.82</v>
       </c>
       <c r="DE50" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF50" t="n">
         <v>1</v>
@@ -25601,7 +25601,7 @@
         <v>1.95</v>
       </c>
       <c r="DE52" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF52" t="n">
         <v>2.2</v>
@@ -27497,7 +27497,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DE56" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -28913,7 +28913,7 @@
         <v>1.18</v>
       </c>
       <c r="DE59" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF59" t="n">
         <v>1</v>
@@ -33214,7 +33214,7 @@
         <v>62</v>
       </c>
       <c r="DD68" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE68" t="n">
         <v>0.76</v>
@@ -33678,7 +33678,7 @@
         <v>79</v>
       </c>
       <c r="DD69" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE69" t="n">
         <v>0.71</v>
@@ -35569,7 +35569,7 @@
         <v>1.58</v>
       </c>
       <c r="DE73" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -38457,7 +38457,7 @@
         <v>1.17</v>
       </c>
       <c r="DE79" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF79" t="n">
         <v>1.5</v>
@@ -38945,7 +38945,7 @@
         <v>1.58</v>
       </c>
       <c r="DE80" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF80" t="n">
         <v>1</v>
@@ -42742,7 +42742,7 @@
         <v>61</v>
       </c>
       <c r="DD88" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE88" t="n">
         <v>1</v>
@@ -43222,7 +43222,7 @@
         <v>89</v>
       </c>
       <c r="DD89" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE89" t="n">
         <v>1.76</v>
@@ -46510,7 +46510,7 @@
         <v>80</v>
       </c>
       <c r="DD96" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE96" t="n">
         <v>0.82</v>
@@ -47921,7 +47921,7 @@
         <v>1.18</v>
       </c>
       <c r="DE99" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF99" t="n">
         <v>0.8</v>
@@ -50774,7 +50774,7 @@
         <v>55</v>
       </c>
       <c r="DD105" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE105" t="n">
         <v>1.95</v>
@@ -51257,7 +51257,7 @@
         <v>0.76</v>
       </c>
       <c r="DE106" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF106" t="n">
         <v>1.09</v>
@@ -54102,7 +54102,7 @@
         <v>71</v>
       </c>
       <c r="DD112" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE112" t="n">
         <v>1</v>
@@ -54247,155 +54247,155 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Juárez</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
         <v>45948.95833333334</v>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>4</v>
       </c>
       <c r="J113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L113" t="n">
         <v>9</v>
       </c>
       <c r="M113" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>7</v>
+      </c>
+      <c r="R113" t="n">
         <v>5</v>
       </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>4</v>
-      </c>
-      <c r="R113" t="n">
-        <v>3</v>
-      </c>
       <c r="S113" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T113" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U113" t="n">
         <v>16</v>
       </c>
       <c r="V113" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W113" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="X113" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Y113" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z113" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Estadio Olímpico Benito Juárez</t>
+          <t>Estadio Nemesio Díez</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Avenida Heroico Colegio Militar, Ciudad Juárez</t>
+          <t>Avenida Constituyentes Poniente No. 1000, Colonia La Merced, Toluca de Lerdo</t>
         </is>
       </c>
       <c r="AC113" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD113" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO113" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF113" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AG113" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK113" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL113" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO113" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AP113" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AR113" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="AS113" t="n">
-        <v>2.81</v>
+        <v>4.7</v>
       </c>
       <c r="AT113" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="AU113" t="n">
         <v>4</v>
       </c>
       <c r="AV113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ113" t="n">
         <v>1</v>
@@ -54404,13 +54404,13 @@
         <v>3</v>
       </c>
       <c r="BB113" t="n">
-        <v>-1</v>
+        <v>1424</v>
       </c>
       <c r="BC113" t="n">
         <v>1</v>
       </c>
       <c r="BD113" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="BE113" t="n">
         <v>0</v>
@@ -54425,182 +54425,182 @@
         <v>1</v>
       </c>
       <c r="BI113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV113" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW113" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX113" t="n">
+        <v>64</v>
+      </c>
+      <c r="BY113" t="n">
+        <v>32</v>
+      </c>
+      <c r="BZ113" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR113" t="n">
         <v>4</v>
       </c>
-      <c r="BJ113" t="n">
-        <v>4</v>
-      </c>
-      <c r="BK113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL113" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM113" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN113" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO113" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ113" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR113" t="n">
+      <c r="CS113" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU113" t="n">
         <v>6</v>
       </c>
-      <c r="BS113" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT113" t="n">
+      <c r="CV113" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX113" t="n">
         <v>9</v>
       </c>
-      <c r="BU113" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV113" t="n">
-        <v>6</v>
-      </c>
-      <c r="BW113" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX113" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY113" t="n">
+      <c r="CY113" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ113" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA113" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB113" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC113" t="n">
+        <v>96</v>
+      </c>
+      <c r="DD113" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DE113" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF113" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DG113" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH113" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI113" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ113" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK113" t="n">
         <v>17</v>
       </c>
-      <c r="BZ113" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CA113" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="CB113" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR113" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS113" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU113" t="n">
+      <c r="DL113" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM113" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DN113" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DO113" t="n">
         <v>17</v>
       </c>
-      <c r="CV113" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX113" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY113" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ113" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA113" t="n">
-        <v>79</v>
-      </c>
-      <c r="DB113" t="n">
-        <v>34</v>
-      </c>
-      <c r="DC113" t="n">
-        <v>79</v>
-      </c>
-      <c r="DD113" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="DE113" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DF113" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG113" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DH113" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DI113" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DJ113" t="n">
-        <v>58</v>
-      </c>
-      <c r="DK113" t="n">
-        <v>21</v>
-      </c>
-      <c r="DL113" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DM113" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DN113" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="DO113" t="n">
-        <v>19</v>
-      </c>
       <c r="DP113" t="b">
         <v>1</v>
       </c>
@@ -54620,104 +54620,80 @@
         <v>0</v>
       </c>
       <c r="DV113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW113" t="n">
-        <v>23.37</v>
+        <v>19.67</v>
       </c>
       <c r="DX113" t="n">
-        <v>5.78</v>
+        <v>2.55</v>
       </c>
       <c r="DY113" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="DZ113" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="EA113" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="EB113" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="EC113" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="ED113" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EE113" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF113" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EG113" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EH113" t="inlineStr">
         <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EI113" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EJ113" t="inlineStr">
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EI113" t="inlineStr"/>
+      <c r="EJ113" t="inlineStr"/>
+      <c r="EK113" t="inlineStr">
         <is>
           <t>1.84</t>
         </is>
       </c>
-      <c r="EK113" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
       <c r="EL113" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EM113" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EN113" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="EO113" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EP113" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM113" t="inlineStr"/>
+      <c r="EN113" t="inlineStr"/>
+      <c r="EO113" t="inlineStr"/>
+      <c r="EP113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -54735,155 +54711,155 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Querétaro</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
         <v>45948.95833333334</v>
       </c>
       <c r="G114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I114" t="n">
         <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L114" t="n">
         <v>9</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R114" t="n">
+        <v>3</v>
+      </c>
+      <c r="S114" t="n">
+        <v>12</v>
+      </c>
+      <c r="T114" t="n">
         <v>5</v>
-      </c>
-      <c r="S114" t="n">
-        <v>9</v>
-      </c>
-      <c r="T114" t="n">
-        <v>9</v>
       </c>
       <c r="U114" t="n">
         <v>16</v>
       </c>
       <c r="V114" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W114" t="n">
+        <v>8</v>
+      </c>
+      <c r="X114" t="n">
         <v>17</v>
       </c>
-      <c r="X114" t="n">
-        <v>7</v>
-      </c>
       <c r="Y114" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="Z114" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Estadio Nemesio Díez</t>
+          <t>Estadio Olímpico Benito Juárez</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Avenida Constituyentes Poniente No. 1000, Colonia La Merced, Toluca de Lerdo</t>
+          <t>Avenida Heroico Colegio Militar, Ciudad Juárez</t>
         </is>
       </c>
       <c r="AC114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AF114" t="n">
-        <v>6.5</v>
+        <v>3.05</v>
       </c>
       <c r="AG114" t="n">
-        <v>9.199999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="AH114" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AI114" t="n">
-        <v>1.33</v>
+        <v>2.01</v>
       </c>
       <c r="AJ114" t="n">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="AK114" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL114" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AM114" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AN114" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AO114" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="AS114" t="n">
-        <v>4.7</v>
+        <v>2.81</v>
       </c>
       <c r="AT114" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="AU114" t="n">
         <v>4</v>
       </c>
       <c r="AV114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ114" t="n">
         <v>1</v>
@@ -54892,13 +54868,13 @@
         <v>3</v>
       </c>
       <c r="BB114" t="n">
-        <v>1424</v>
+        <v>-1</v>
       </c>
       <c r="BC114" t="n">
         <v>1</v>
       </c>
       <c r="BD114" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="BE114" t="n">
         <v>0</v>
@@ -54913,181 +54889,181 @@
         <v>1</v>
       </c>
       <c r="BI114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>6</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW114" t="n">
         <v>5</v>
       </c>
-      <c r="BM114" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN114" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV114" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW114" t="n">
+      <c r="BX114" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>17</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR114" t="n">
         <v>13</v>
       </c>
-      <c r="BX114" t="n">
-        <v>64</v>
-      </c>
-      <c r="BY114" t="n">
-        <v>32</v>
-      </c>
-      <c r="BZ114" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CA114" t="n">
+      <c r="CS114" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU114" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX114" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY114" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ114" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA114" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB114" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC114" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD114" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DE114" t="n">
         <v>1.32</v>
       </c>
-      <c r="CB114" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CC114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR114" t="n">
-        <v>4</v>
-      </c>
-      <c r="CS114" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU114" t="n">
-        <v>6</v>
-      </c>
-      <c r="CV114" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX114" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY114" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ114" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA114" t="n">
-        <v>84</v>
-      </c>
-      <c r="DB114" t="n">
-        <v>46</v>
-      </c>
-      <c r="DC114" t="n">
-        <v>96</v>
-      </c>
-      <c r="DD114" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE114" t="n">
-        <v>1.18</v>
-      </c>
       <c r="DF114" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="DG114" t="n">
-        <v>0.92</v>
+        <v>1.67</v>
       </c>
       <c r="DH114" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="DI114" t="n">
-        <v>0.92</v>
+        <v>1.67</v>
       </c>
       <c r="DJ114" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="DK114" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="DL114" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="DM114" t="n">
-        <v>0.88</v>
+        <v>1.57</v>
       </c>
       <c r="DN114" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="DO114" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -55108,80 +55084,104 @@
         <v>0</v>
       </c>
       <c r="DV114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW114" t="n">
-        <v>19.67</v>
+        <v>23.37</v>
       </c>
       <c r="DX114" t="n">
-        <v>2.55</v>
+        <v>5.78</v>
       </c>
       <c r="DY114" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="DZ114" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="EA114" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EB114" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EC114" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="ED114" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EE114" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EF114" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EG114" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EH114" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EI114" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EE114" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF114" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EG114" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EH114" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EI114" t="inlineStr"/>
-      <c r="EJ114" t="inlineStr"/>
+      <c r="EJ114" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="EK114" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EL114" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM114" t="inlineStr"/>
-      <c r="EN114" t="inlineStr"/>
-      <c r="EO114" t="inlineStr"/>
-      <c r="EP114" t="inlineStr"/>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM114" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EN114" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EO114" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EP114" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -58923,12 +58923,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
@@ -58938,155 +58938,155 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L123" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>4</v>
+      </c>
+      <c r="R123" t="n">
+        <v>4</v>
+      </c>
+      <c r="S123" t="n">
+        <v>2</v>
+      </c>
+      <c r="T123" t="n">
+        <v>18</v>
+      </c>
+      <c r="U123" t="n">
+        <v>6</v>
+      </c>
+      <c r="V123" t="n">
+        <v>22</v>
+      </c>
+      <c r="W123" t="n">
+        <v>10</v>
+      </c>
+      <c r="X123" t="n">
         <v>7</v>
       </c>
-      <c r="O123" t="n">
-        <v>2</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>5</v>
-      </c>
-      <c r="R123" t="n">
-        <v>8</v>
-      </c>
-      <c r="S123" t="n">
-        <v>15</v>
-      </c>
-      <c r="T123" t="n">
-        <v>3</v>
-      </c>
-      <c r="U123" t="n">
-        <v>20</v>
-      </c>
-      <c r="V123" t="n">
-        <v>11</v>
-      </c>
-      <c r="W123" t="n">
-        <v>9</v>
-      </c>
-      <c r="X123" t="n">
-        <v>15</v>
-      </c>
       <c r="Y123" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="Z123" t="n">
+        <v>74</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>Estadio La Corregidora</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>Avenida Luis Vega Monroy 409-4, Santiago de Querétaro</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>1427</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD123" t="n">
         <v>46</v>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>Estadio Hidalgo</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>Boulevard Felipe Angeles, Pachuca de Soto</t>
-        </is>
-      </c>
-      <c r="AC123" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AF123" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG123" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AK123" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL123" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM123" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN123" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO123" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AP123" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AQ123" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR123" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT123" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AU123" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY123" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB123" t="n">
-        <v>1423</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>42</v>
       </c>
       <c r="BE123" t="n">
         <v>0</v>
@@ -59101,190 +59101,190 @@
         <v>1</v>
       </c>
       <c r="BI123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>99</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>41</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>143</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
         <v>7</v>
       </c>
-      <c r="BL123" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM123" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN123" t="n">
+      <c r="CV123" t="n">
         <v>10</v>
       </c>
-      <c r="BO123" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP123" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ123" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR123" t="n">
-        <v>6</v>
-      </c>
-      <c r="BS123" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT123" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU123" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV123" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW123" t="n">
-        <v>26</v>
-      </c>
-      <c r="BX123" t="n">
-        <v>102</v>
-      </c>
-      <c r="BY123" t="n">
-        <v>80</v>
-      </c>
-      <c r="BZ123" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CA123" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CB123" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="CC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR123" t="n">
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
         <v>19</v>
       </c>
-      <c r="CS123" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU123" t="n">
+      <c r="CY123" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ123" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC123" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD123" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DE123" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DF123" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DG123" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DH123" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DI123" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DJ123" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK123" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL123" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DM123" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN123" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DO123" t="n">
         <v>17</v>
       </c>
-      <c r="CV123" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX123" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY123" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ123" t="n">
-        <v>42</v>
-      </c>
-      <c r="DA123" t="n">
-        <v>73</v>
-      </c>
-      <c r="DB123" t="n">
-        <v>46</v>
-      </c>
-      <c r="DC123" t="n">
-        <v>66</v>
-      </c>
-      <c r="DD123" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DE123" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF123" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DG123" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH123" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DI123" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ123" t="n">
-        <v>58</v>
-      </c>
-      <c r="DK123" t="n">
-        <v>27</v>
-      </c>
-      <c r="DL123" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="DM123" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DN123" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="DO123" t="n">
-        <v>19</v>
-      </c>
       <c r="DP123" t="b">
         <v>1</v>
       </c>
       <c r="DQ123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS123" t="b">
         <v>0</v>
@@ -59296,104 +59296,88 @@
         <v>0</v>
       </c>
       <c r="DV123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW123" t="n">
-        <v>20.39</v>
+        <v>24.14</v>
       </c>
       <c r="DX123" t="n">
-        <v>5.54</v>
+        <v>3.5</v>
       </c>
       <c r="DY123" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="DZ123" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA123" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EB123" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EC123" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="ED123" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="EE123" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EF123" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EG123" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr"/>
+      <c r="EJ123" t="inlineStr"/>
+      <c r="EK123" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="EH123" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EI123" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EJ123" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EK123" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
       <c r="EL123" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EM123" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EN123" t="inlineStr">
         <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="EO123" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EP123" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EO123" t="inlineStr"/>
+      <c r="EP123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -59411,12 +59395,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Querétaro</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Tigres UANL</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
@@ -59426,155 +59410,155 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K124" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" t="n">
+        <v>12</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3</v>
+      </c>
+      <c r="N124" t="n">
+        <v>7</v>
+      </c>
+      <c r="O124" t="n">
+        <v>2</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>5</v>
+      </c>
+      <c r="R124" t="n">
+        <v>8</v>
+      </c>
+      <c r="S124" t="n">
+        <v>15</v>
+      </c>
+      <c r="T124" t="n">
+        <v>3</v>
+      </c>
+      <c r="U124" t="n">
+        <v>20</v>
+      </c>
+      <c r="V124" t="n">
         <v>11</v>
       </c>
-      <c r="L124" t="n">
-        <v>11</v>
-      </c>
-      <c r="M124" t="n">
-        <v>2</v>
-      </c>
-      <c r="N124" t="n">
-        <v>1</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>4</v>
-      </c>
-      <c r="R124" t="n">
-        <v>4</v>
-      </c>
-      <c r="S124" t="n">
-        <v>2</v>
-      </c>
-      <c r="T124" t="n">
-        <v>18</v>
-      </c>
-      <c r="U124" t="n">
-        <v>6</v>
-      </c>
-      <c r="V124" t="n">
-        <v>22</v>
-      </c>
       <c r="W124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X124" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Y124" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="Z124" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>Estadio La Corregidora</t>
+          <t>Estadio Hidalgo</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Avenida Luis Vega Monroy 409-4, Santiago de Querétaro</t>
+          <t>Boulevard Felipe Angeles, Pachuca de Soto</t>
         </is>
       </c>
       <c r="AC124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE124" t="n">
-        <v>4.33</v>
+        <v>2.79</v>
       </c>
       <c r="AF124" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AG124" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AI124" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AJ124" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AK124" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AL124" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AM124" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AN124" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AO124" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR124" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS124" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AT124" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AU124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW124" t="n">
         <v>0</v>
       </c>
       <c r="AX124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB124" t="n">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="BC124" t="n">
         <v>1</v>
       </c>
       <c r="BD124" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BE124" t="n">
         <v>0</v>
@@ -59589,190 +59573,190 @@
         <v>1</v>
       </c>
       <c r="BI124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR124" t="n">
         <v>6</v>
       </c>
-      <c r="BK124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL124" t="n">
+      <c r="BS124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
         <v>5</v>
       </c>
-      <c r="BM124" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN124" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ124" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT124" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV124" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW124" t="n">
-        <v>99</v>
-      </c>
-      <c r="BX124" t="n">
-        <v>41</v>
-      </c>
-      <c r="BY124" t="n">
-        <v>143</v>
-      </c>
-      <c r="BZ124" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA124" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CB124" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR124" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS124" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU124" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV124" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX124" t="n">
+      <c r="CY124" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ124" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DO124" t="n">
         <v>19</v>
       </c>
-      <c r="CY124" t="n">
-        <v>5</v>
-      </c>
-      <c r="CZ124" t="n">
-        <v>58</v>
-      </c>
-      <c r="DA124" t="n">
-        <v>77</v>
-      </c>
-      <c r="DB124" t="n">
-        <v>42</v>
-      </c>
-      <c r="DC124" t="n">
-        <v>85</v>
-      </c>
-      <c r="DD124" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DE124" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DF124" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="DG124" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DH124" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="DI124" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DJ124" t="n">
-        <v>42</v>
-      </c>
-      <c r="DK124" t="n">
-        <v>23</v>
-      </c>
-      <c r="DL124" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DM124" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DN124" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DO124" t="n">
-        <v>17</v>
-      </c>
       <c r="DP124" t="b">
         <v>1</v>
       </c>
       <c r="DQ124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS124" t="b">
         <v>0</v>
@@ -59784,88 +59768,104 @@
         <v>0</v>
       </c>
       <c r="DV124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW124" t="n">
-        <v>24.14</v>
+        <v>20.39</v>
       </c>
       <c r="DX124" t="n">
-        <v>3.5</v>
+        <v>5.54</v>
       </c>
       <c r="DY124" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ124" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EC124" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="ED124" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EE124" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EF124" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EG124" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EH124" t="inlineStr">
         <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EM124" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EN124" t="inlineStr">
+        <is>
           <t>3.28</t>
         </is>
       </c>
-      <c r="EI124" t="inlineStr"/>
-      <c r="EJ124" t="inlineStr"/>
-      <c r="EK124" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EL124" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM124" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EN124" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="EO124" t="inlineStr"/>
-      <c r="EP124" t="inlineStr"/>
+      <c r="EO124" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EP124" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -59883,170 +59883,170 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>León</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
         <v>45953.125</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K125" t="n">
+        <v>6</v>
+      </c>
+      <c r="L125" t="n">
+        <v>9</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
         <v>5</v>
       </c>
-      <c r="L125" t="n">
-        <v>7</v>
-      </c>
-      <c r="M125" t="n">
-        <v>2</v>
-      </c>
-      <c r="N125" t="n">
-        <v>1</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U125" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="V125" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W125" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X125" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y125" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Z125" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Estadio Caliente</t>
+          <t>Estadio Jalisco</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>Boulevard Agua Caliente 12027, Colonia Hipódromo, Tijuana</t>
+          <t>Calle 7 Colinas No. 1772, Colonia Independencia, Guadalajara</t>
         </is>
       </c>
       <c r="AC125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE125" t="n">
-        <v>3.07</v>
+        <v>2.65</v>
       </c>
       <c r="AF125" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AG125" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AI125" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AJ125" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="AK125" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AL125" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AM125" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AN125" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AO125" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.25</v>
       </c>
       <c r="AR125" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AS125" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AT125" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AU125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW125" t="n">
         <v>0</v>
       </c>
       <c r="AX125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY125" t="n">
         <v>0</v>
       </c>
       <c r="AZ125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB125" t="n">
-        <v>-1</v>
+        <v>1421</v>
       </c>
       <c r="BC125" t="n">
         <v>1</v>
       </c>
       <c r="BD125" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="BE125" t="n">
         <v>0</v>
@@ -60055,193 +60055,193 @@
         <v>-1</v>
       </c>
       <c r="BG125" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH125" t="n">
         <v>1</v>
       </c>
       <c r="BI125" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ125" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BK125" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL125" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BM125" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BN125" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BO125" t="n">
         <v>0</v>
       </c>
       <c r="BP125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU125" t="n">
         <v>1</v>
       </c>
       <c r="BV125" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BW125" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="BX125" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="BY125" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="BZ125" t="n">
-        <v>0.49</v>
+        <v>1.32</v>
       </c>
       <c r="CA125" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>54</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL125" t="n">
         <v>1.07</v>
       </c>
-      <c r="CB125" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM125" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN125" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP125" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR125" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS125" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU125" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV125" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX125" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY125" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ125" t="n">
-        <v>66</v>
-      </c>
-      <c r="DA125" t="n">
-        <v>89</v>
-      </c>
-      <c r="DB125" t="n">
-        <v>43</v>
-      </c>
-      <c r="DC125" t="n">
-        <v>85</v>
-      </c>
-      <c r="DD125" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE125" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF125" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DG125" t="n">
+      <c r="DM125" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN125" t="n">
         <v>2.38</v>
       </c>
-      <c r="DH125" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DI125" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DJ125" t="n">
-        <v>35</v>
-      </c>
-      <c r="DK125" t="n">
-        <v>12</v>
-      </c>
-      <c r="DL125" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DM125" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="DN125" t="n">
-        <v>3.18</v>
-      </c>
       <c r="DO125" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="DP125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR125" t="b">
         <v>0</v>
@@ -60259,93 +60259,85 @@
         <v>0</v>
       </c>
       <c r="DW125" t="n">
-        <v>21.53</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DX125" t="n">
-        <v>3.45</v>
+        <v>6.65</v>
       </c>
       <c r="DY125" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="DZ125" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="EA125" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EB125" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="EC125" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED125" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EE125" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EF125" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EG125" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EH125" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="EI125" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EJ125" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EK125" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EL125" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="EM125" t="inlineStr"/>
       <c r="EN125" t="inlineStr"/>
-      <c r="EO125" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EP125" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
+      <c r="EO125" t="inlineStr"/>
+      <c r="EP125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -60363,170 +60355,170 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>León</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
         <v>45953.125</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L126" t="n">
+        <v>7</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" t="n">
+        <v>4</v>
+      </c>
+      <c r="T126" t="n">
+        <v>7</v>
+      </c>
+      <c r="U126" t="n">
+        <v>4</v>
+      </c>
+      <c r="V126" t="n">
         <v>9</v>
       </c>
-      <c r="M126" t="n">
-        <v>1</v>
-      </c>
-      <c r="N126" t="n">
-        <v>3</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>5</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>6</v>
-      </c>
-      <c r="T126" t="n">
-        <v>6</v>
-      </c>
-      <c r="U126" t="n">
-        <v>11</v>
-      </c>
-      <c r="V126" t="n">
-        <v>6</v>
-      </c>
       <c r="W126" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X126" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y126" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Z126" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>Estadio Jalisco</t>
+          <t>Estadio Caliente</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>Calle 7 Colinas No. 1772, Colonia Independencia, Guadalajara</t>
+          <t>Boulevard Agua Caliente 12027, Colonia Hipódromo, Tijuana</t>
         </is>
       </c>
       <c r="AC126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE126" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="AF126" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AG126" t="n">
-        <v>2.61</v>
+        <v>2.1</v>
       </c>
       <c r="AH126" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AI126" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="AJ126" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AK126" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL126" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AM126" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AN126" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AO126" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AP126" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.25</v>
       </c>
       <c r="AR126" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AS126" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT126" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AU126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW126" t="n">
         <v>0</v>
       </c>
       <c r="AX126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY126" t="n">
         <v>0</v>
       </c>
       <c r="AZ126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB126" t="n">
-        <v>1421</v>
+        <v>-1</v>
       </c>
       <c r="BC126" t="n">
         <v>1</v>
       </c>
       <c r="BD126" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="BE126" t="n">
         <v>0</v>
@@ -60535,193 +60527,193 @@
         <v>-1</v>
       </c>
       <c r="BG126" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH126" t="n">
         <v>1</v>
       </c>
       <c r="BI126" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BJ126" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BK126" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL126" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BM126" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BN126" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BO126" t="n">
         <v>0</v>
       </c>
       <c r="BP126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>127</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
         <v>4</v>
       </c>
-      <c r="BU126" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV126" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW126" t="n">
-        <v>39</v>
-      </c>
-      <c r="BX126" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY126" t="n">
-        <v>77</v>
-      </c>
-      <c r="BZ126" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CA126" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="CB126" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CC126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR126" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS126" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU126" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV126" t="n">
-        <v>18</v>
-      </c>
-      <c r="CW126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX126" t="n">
-        <v>6</v>
-      </c>
       <c r="CY126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CZ126" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="DA126" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="DB126" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="DC126" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="DD126" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DE126" t="n">
-        <v>0.76</v>
+        <v>2.04</v>
       </c>
       <c r="DF126" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="DG126" t="n">
-        <v>0.92</v>
+        <v>2.38</v>
       </c>
       <c r="DH126" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="DI126" t="n">
-        <v>0.92</v>
+        <v>2.38</v>
       </c>
       <c r="DJ126" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="DK126" t="n">
+        <v>12</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="DO126" t="n">
         <v>20</v>
       </c>
-      <c r="DL126" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="DM126" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DN126" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DO126" t="n">
-        <v>17</v>
-      </c>
       <c r="DP126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR126" t="b">
         <v>0</v>
@@ -60739,85 +60731,93 @@
         <v>0</v>
       </c>
       <c r="DW126" t="n">
-        <v>9.869999999999999</v>
+        <v>21.53</v>
       </c>
       <c r="DX126" t="n">
-        <v>6.65</v>
+        <v>3.45</v>
       </c>
       <c r="DY126" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ126" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA126" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EB126" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EC126" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="ED126" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EE126" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EF126" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EG126" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EH126" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EI126" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ126" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EK126" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL126" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EM126" t="inlineStr"/>
       <c r="EN126" t="inlineStr"/>
-      <c r="EO126" t="inlineStr"/>
-      <c r="EP126" t="inlineStr"/>
+      <c r="EO126" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EP126" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -62582,7 +62582,7 @@
         <v>61</v>
       </c>
       <c r="DD130" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE130" t="n">
         <v>1.5</v>
@@ -64655,46 +64655,46 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Atlético San Luis</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>45957.04166666666</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I135" t="n">
+        <v>7</v>
+      </c>
+      <c r="J135" t="n">
         <v>4</v>
       </c>
-      <c r="J135" t="n">
-        <v>6</v>
-      </c>
       <c r="K135" t="n">
         <v>3</v>
       </c>
       <c r="L135" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
         <v>4</v>
@@ -64703,122 +64703,122 @@
         <v>6</v>
       </c>
       <c r="S135" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="T135" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U135" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V135" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W135" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X135" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y135" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z135" t="n">
         <v>59</v>
       </c>
-      <c r="Z135" t="n">
-        <v>41</v>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Estadio Nemesio Díez</t>
+          <t>Estadio Alfonso Lastras Ramírez</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Avenida Constituyentes Poniente No. 1000, Colonia La Merced, Toluca de Lerdo</t>
+          <t xml:space="preserve">, </t>
         </is>
       </c>
       <c r="AC135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD135" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE135" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK135" t="n">
         <v>1.52</v>
       </c>
-      <c r="AF135" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK135" t="n">
+      <c r="AL135" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT135" t="n">
         <v>1.55</v>
       </c>
-      <c r="AL135" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AU135" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY135" t="n">
         <v>4</v>
       </c>
-      <c r="AV135" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>1</v>
-      </c>
       <c r="AZ135" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BA135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB135" t="n">
-        <v>-1</v>
+        <v>1428</v>
       </c>
       <c r="BC135" t="n">
         <v>1</v>
       </c>
       <c r="BD135" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
@@ -64833,181 +64833,181 @@
         <v>1</v>
       </c>
       <c r="BI135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK135" t="n">
         <v>3</v>
       </c>
       <c r="BL135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM135" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BN135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO135" t="n">
         <v>1</v>
       </c>
       <c r="BP135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR135" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>56</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY135" t="n">
         <v>7</v>
       </c>
-      <c r="BU135" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV135" t="n">
-        <v>59</v>
-      </c>
-      <c r="BW135" t="n">
-        <v>41</v>
-      </c>
-      <c r="BX135" t="n">
+      <c r="CZ135" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA135" t="n">
         <v>75</v>
       </c>
-      <c r="BY135" t="n">
-        <v>62</v>
-      </c>
-      <c r="BZ135" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA135" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CB135" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="CC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL135" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO135" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP135" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR135" t="n">
-        <v>11</v>
-      </c>
-      <c r="CS135" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU135" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV135" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW135" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX135" t="n">
-        <v>13</v>
-      </c>
-      <c r="CY135" t="n">
-        <v>17</v>
-      </c>
-      <c r="CZ135" t="n">
-        <v>61</v>
-      </c>
-      <c r="DA135" t="n">
-        <v>83</v>
-      </c>
       <c r="DB135" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="DC135" t="n">
         <v>79</v>
       </c>
       <c r="DD135" t="n">
-        <v>2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="DF135" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.5</v>
+        <v>0.71</v>
       </c>
       <c r="DH135" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.5</v>
+        <v>0.71</v>
       </c>
       <c r="DJ135" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DK135" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="DN135" t="n">
-        <v>3.34</v>
+        <v>2.84</v>
       </c>
       <c r="DO135" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65022,94 +65022,94 @@
         <v>1</v>
       </c>
       <c r="DT135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV135" t="b">
         <v>1</v>
       </c>
       <c r="DW135" t="n">
-        <v>19.38</v>
+        <v>24.69</v>
       </c>
       <c r="DX135" t="n">
-        <v>4.07</v>
+        <v>5.68</v>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA135" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EB135" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EC135" t="inlineStr">
         <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="ED135" t="inlineStr"/>
-      <c r="EE135" t="inlineStr"/>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="ED135" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
       <c r="EF135" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EG135" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EH135" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EI135" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EJ135" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EK135" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EL135" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EM135" t="inlineStr"/>
       <c r="EN135" t="inlineStr"/>
-      <c r="EO135" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EP135" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
+      <c r="EO135" t="inlineStr"/>
+      <c r="EP135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -65127,46 +65127,46 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Atlético San Luis</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="F136" s="2" t="n">
         <v>45957.04166666666</v>
       </c>
       <c r="G136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="n">
         <v>4</v>
       </c>
-      <c r="I136" t="n">
-        <v>7</v>
-      </c>
       <c r="J136" t="n">
+        <v>6</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" t="n">
+        <v>9</v>
+      </c>
+      <c r="M136" t="n">
+        <v>3</v>
+      </c>
+      <c r="N136" t="n">
         <v>4</v>
       </c>
-      <c r="K136" t="n">
-        <v>3</v>
-      </c>
-      <c r="L136" t="n">
-        <v>7</v>
-      </c>
-      <c r="M136" t="n">
-        <v>2</v>
-      </c>
-      <c r="N136" t="n">
-        <v>2</v>
-      </c>
       <c r="O136" t="n">
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q136" t="n">
         <v>4</v>
@@ -65175,122 +65175,122 @@
         <v>6</v>
       </c>
       <c r="S136" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T136" t="n">
+        <v>10</v>
+      </c>
+      <c r="U136" t="n">
+        <v>20</v>
+      </c>
+      <c r="V136" t="n">
+        <v>16</v>
+      </c>
+      <c r="W136" t="n">
         <v>8</v>
       </c>
-      <c r="U136" t="n">
-        <v>11</v>
-      </c>
-      <c r="V136" t="n">
-        <v>14</v>
-      </c>
-      <c r="W136" t="n">
+      <c r="X136" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Díez</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>Avenida Constituyentes Poniente No. 1000, Colonia La Merced, Toluca de Lerdo</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD136" t="n">
         <v>5</v>
       </c>
-      <c r="X136" t="n">
+      <c r="AE136" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU136" t="n">
         <v>4</v>
       </c>
-      <c r="Y136" t="n">
-        <v>41</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>Estadio Alfonso Lastras Ramírez</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">, </t>
-        </is>
-      </c>
-      <c r="AC136" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE136" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AK136" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AL136" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM136" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN136" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO136" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AP136" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AQ136" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR136" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS136" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AT136" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AU136" t="n">
-        <v>7</v>
-      </c>
       <c r="AV136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AZ136" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BA136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB136" t="n">
-        <v>1428</v>
+        <v>-1</v>
       </c>
       <c r="BC136" t="n">
         <v>1</v>
       </c>
       <c r="BD136" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="BE136" t="n">
         <v>0</v>
@@ -65305,76 +65305,76 @@
         <v>1</v>
       </c>
       <c r="BI136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK136" t="n">
         <v>3</v>
       </c>
       <c r="BL136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM136" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BN136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO136" t="n">
         <v>1</v>
       </c>
       <c r="BP136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR136" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT136" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BU136" t="n">
         <v>1</v>
       </c>
       <c r="BV136" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="BW136" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BX136" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="BY136" t="n">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="BZ136" t="n">
-        <v>1.19</v>
+        <v>1.96</v>
       </c>
       <c r="CA136" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="CB136" t="n">
-        <v>2.79</v>
+        <v>3.67</v>
       </c>
       <c r="CC136" t="n">
         <v>0</v>
       </c>
       <c r="CD136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE136" t="n">
         <v>0</v>
       </c>
       <c r="CF136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG136" t="n">
         <v>0</v>
@@ -65389,7 +65389,7 @@
         <v>1</v>
       </c>
       <c r="CK136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL136" t="n">
         <v>0</v>
@@ -65398,10 +65398,10 @@
         <v>1</v>
       </c>
       <c r="CN136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP136" t="n">
         <v>0</v>
@@ -65410,76 +65410,76 @@
         <v>1</v>
       </c>
       <c r="CR136" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="CS136" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="CT136" t="n">
         <v>1</v>
       </c>
       <c r="CU136" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CV136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
         <v>13</v>
       </c>
-      <c r="CW136" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX136" t="n">
-        <v>12</v>
-      </c>
       <c r="CY136" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="CZ136" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="DA136" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="DB136" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="DC136" t="n">
         <v>79</v>
       </c>
       <c r="DD136" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="DE136" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="DF136" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="DG136" t="n">
-        <v>0.71</v>
+        <v>1.5</v>
       </c>
       <c r="DH136" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="DI136" t="n">
-        <v>0.71</v>
+        <v>1.5</v>
       </c>
       <c r="DJ136" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DK136" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="DL136" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="DM136" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DN136" t="n">
-        <v>2.84</v>
+        <v>3.34</v>
       </c>
       <c r="DO136" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -65494,94 +65494,94 @@
         <v>1</v>
       </c>
       <c r="DT136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV136" t="b">
         <v>1</v>
       </c>
       <c r="DW136" t="n">
-        <v>24.69</v>
+        <v>19.38</v>
       </c>
       <c r="DX136" t="n">
-        <v>5.68</v>
+        <v>4.07</v>
       </c>
       <c r="DY136" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="DZ136" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="EA136" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="EB136" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="EC136" t="inlineStr">
         <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED136" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="EE136" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED136" t="inlineStr"/>
+      <c r="EE136" t="inlineStr"/>
       <c r="EF136" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EG136" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EH136" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EI136" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ136" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EK136" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EL136" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EM136" t="inlineStr"/>
       <c r="EN136" t="inlineStr"/>
-      <c r="EO136" t="inlineStr"/>
-      <c r="EP136" t="inlineStr"/>
+      <c r="EO136" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EP136" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -67345,7 +67345,7 @@
         <v>1</v>
       </c>
       <c r="DE140" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF140" t="n">
         <v>1.07</v>
@@ -67825,7 +67825,7 @@
         <v>1.76</v>
       </c>
       <c r="DE141" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF141" t="n">
         <v>2</v>
@@ -70343,162 +70343,170 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mazatlán</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="F147" s="2" t="n">
         <v>45969.125</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
         <v>2</v>
       </c>
       <c r="J147" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K147" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M147" t="n">
         <v>5</v>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
+        <v>14</v>
+      </c>
+      <c r="T147" t="n">
+        <v>6</v>
+      </c>
+      <c r="U147" t="n">
+        <v>24</v>
+      </c>
+      <c r="V147" t="n">
+        <v>7</v>
+      </c>
+      <c r="W147" t="n">
         <v>5</v>
       </c>
-      <c r="S147" t="n">
-        <v>3</v>
-      </c>
-      <c r="T147" t="n">
-        <v>17</v>
-      </c>
-      <c r="U147" t="n">
+      <c r="X147" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>Estadio Caliente</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>Boulevard Agua Caliente 12027, Colonia Hipódromo, Tijuana</t>
+        </is>
+      </c>
+      <c r="AC147" t="n">
         <v>5</v>
       </c>
-      <c r="V147" t="n">
-        <v>22</v>
-      </c>
-      <c r="W147" t="n">
-        <v>3</v>
-      </c>
-      <c r="X147" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>69</v>
-      </c>
-      <c r="AA147" t="inlineStr"/>
-      <c r="AB147" t="inlineStr"/>
-      <c r="AC147" t="n">
-        <v>7</v>
-      </c>
       <c r="AD147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE147" t="n">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="AF147" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG147" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AH147" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AI147" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ147" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AK147" t="n">
         <v>1.5</v>
       </c>
       <c r="AL147" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AM147" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AN147" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AO147" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AR147" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AS147" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="AT147" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AU147" t="n">
         <v>2</v>
       </c>
       <c r="AV147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW147" t="n">
         <v>0</v>
       </c>
       <c r="AX147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB147" t="n">
-        <v>-1</v>
+        <v>1418</v>
       </c>
       <c r="BC147" t="n">
         <v>1</v>
       </c>
       <c r="BD147" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="BE147" t="n">
         <v>0</v>
@@ -70513,73 +70521,73 @@
         <v>1</v>
       </c>
       <c r="BI147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL147" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BM147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN147" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="BO147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BP147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BR147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS147" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT147" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BU147" t="n">
         <v>1</v>
       </c>
       <c r="BV147" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BW147" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="BX147" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="BY147" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="BZ147" t="n">
-        <v>0.68</v>
+        <v>2.6</v>
       </c>
       <c r="CA147" t="n">
-        <v>2.41</v>
+        <v>0.77</v>
       </c>
       <c r="CB147" t="n">
-        <v>3.09</v>
+        <v>3.37</v>
       </c>
       <c r="CC147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD147" t="n">
         <v>0</v>
       </c>
       <c r="CE147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF147" t="n">
         <v>0</v>
@@ -70603,13 +70611,13 @@
         <v>0</v>
       </c>
       <c r="CM147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN147" t="n">
         <v>0</v>
       </c>
       <c r="CO147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP147" t="n">
         <v>0</v>
@@ -70618,73 +70626,73 @@
         <v>1</v>
       </c>
       <c r="CR147" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS147" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU147" t="n">
         <v>9</v>
       </c>
-      <c r="CS147" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT147" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU147" t="n">
-        <v>22</v>
-      </c>
       <c r="CV147" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW147" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX147" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY147" t="n">
         <v>10</v>
       </c>
-      <c r="CW147" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX147" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY147" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ147" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="DA147" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="DB147" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="DC147" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="DD147" t="n">
-        <v>0.82</v>
+        <v>1.5</v>
       </c>
       <c r="DE147" t="n">
         <v>1</v>
       </c>
       <c r="DF147" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="DG147" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DH147" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="DI147" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DJ147" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="DK147" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="DL147" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="DM147" t="n">
-        <v>1.66</v>
+        <v>1.09</v>
       </c>
       <c r="DN147" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="DO147" t="n">
         <v>17</v>
@@ -70708,17 +70716,17 @@
         <v>0</v>
       </c>
       <c r="DV147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW147" t="n">
-        <v>27.25</v>
+        <v>25.09</v>
       </c>
       <c r="DX147" t="n">
-        <v>4.14</v>
+        <v>3.31</v>
       </c>
       <c r="DY147" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ147" t="inlineStr">
@@ -70728,60 +70736,76 @@
       </c>
       <c r="EA147" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EB147" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="EC147" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="ED147" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EE147" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EF147" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="EG147" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EH147" t="inlineStr">
         <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="EI147" t="inlineStr"/>
-      <c r="EJ147" t="inlineStr"/>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EI147" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ147" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
       <c r="EK147" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL147" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EM147" t="inlineStr"/>
       <c r="EN147" t="inlineStr"/>
-      <c r="EO147" t="inlineStr"/>
-      <c r="EP147" t="inlineStr"/>
+      <c r="EO147" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EP147" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -70799,170 +70823,162 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
         <v>45969.125</v>
       </c>
       <c r="G148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" t="n">
         <v>2</v>
       </c>
       <c r="J148" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L148" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M148" t="n">
         <v>5</v>
       </c>
       <c r="N148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R148" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S148" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T148" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="U148" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="V148" t="n">
+        <v>22</v>
+      </c>
+      <c r="W148" t="n">
+        <v>3</v>
+      </c>
+      <c r="X148" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA148" t="inlineStr"/>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="n">
         <v>7</v>
       </c>
-      <c r="W148" t="n">
-        <v>5</v>
-      </c>
-      <c r="X148" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Estadio Caliente</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>Boulevard Agua Caliente 12027, Colonia Hipódromo, Tijuana</t>
-        </is>
-      </c>
-      <c r="AC148" t="n">
-        <v>5</v>
-      </c>
       <c r="AD148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.63</v>
+        <v>3.15</v>
       </c>
       <c r="AF148" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AG148" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ148" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AK148" t="n">
         <v>1.5</v>
       </c>
       <c r="AL148" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="AM148" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AO148" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AR148" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AS148" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="AT148" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AU148" t="n">
         <v>2</v>
       </c>
       <c r="AV148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW148" t="n">
         <v>0</v>
       </c>
       <c r="AX148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB148" t="n">
-        <v>1418</v>
+        <v>-1</v>
       </c>
       <c r="BC148" t="n">
         <v>1</v>
       </c>
       <c r="BD148" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="BE148" t="n">
         <v>0</v>
@@ -70977,73 +70993,73 @@
         <v>1</v>
       </c>
       <c r="BI148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL148" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BM148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN148" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="BO148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BR148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BT148" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BU148" t="n">
         <v>1</v>
       </c>
       <c r="BV148" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BW148" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="BX148" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="BY148" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="BZ148" t="n">
-        <v>2.6</v>
+        <v>0.68</v>
       </c>
       <c r="CA148" t="n">
-        <v>0.77</v>
+        <v>2.41</v>
       </c>
       <c r="CB148" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="CC148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD148" t="n">
         <v>0</v>
       </c>
       <c r="CE148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF148" t="n">
         <v>0</v>
@@ -71067,13 +71083,13 @@
         <v>0</v>
       </c>
       <c r="CM148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN148" t="n">
         <v>0</v>
       </c>
       <c r="CO148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP148" t="n">
         <v>0</v>
@@ -71082,73 +71098,73 @@
         <v>1</v>
       </c>
       <c r="CR148" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="CS148" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CT148" t="n">
         <v>1</v>
       </c>
       <c r="CU148" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV148" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW148" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX148" t="n">
         <v>9</v>
       </c>
-      <c r="CV148" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW148" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX148" t="n">
-        <v>7</v>
-      </c>
       <c r="CY148" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="CZ148" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="DA148" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="DB148" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="DC148" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="DD148" t="n">
-        <v>1.5</v>
+        <v>0.82</v>
       </c>
       <c r="DE148" t="n">
         <v>1</v>
       </c>
       <c r="DF148" t="n">
-        <v>1.31</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DG148" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DH148" t="n">
-        <v>1.31</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DI148" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DJ148" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="DK148" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="DL148" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="DM148" t="n">
-        <v>1.09</v>
+        <v>1.66</v>
       </c>
       <c r="DN148" t="n">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="DO148" t="n">
         <v>17</v>
@@ -71172,17 +71188,17 @@
         <v>0</v>
       </c>
       <c r="DV148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW148" t="n">
-        <v>25.09</v>
+        <v>27.25</v>
       </c>
       <c r="DX148" t="n">
-        <v>3.31</v>
+        <v>4.14</v>
       </c>
       <c r="DY148" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ148" t="inlineStr">
@@ -71192,76 +71208,60 @@
       </c>
       <c r="EA148" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="EB148" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC148" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="ED148" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EE148" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EF148" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EG148" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EH148" t="inlineStr">
         <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EI148" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EJ148" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EI148" t="inlineStr"/>
+      <c r="EJ148" t="inlineStr"/>
       <c r="EK148" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL148" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="EM148" t="inlineStr"/>
       <c r="EN148" t="inlineStr"/>
-      <c r="EO148" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EP148" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
+      <c r="EO148" t="inlineStr"/>
+      <c r="EP148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -71598,7 +71598,7 @@
         <v>57</v>
       </c>
       <c r="DD149" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE149" t="n">
         <v>0.9399999999999999</v>
@@ -72239,41 +72239,41 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>León</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>América</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
         <v>45970.04166666666</v>
       </c>
       <c r="G151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
+        <v>6</v>
+      </c>
+      <c r="K151" t="n">
+        <v>7</v>
+      </c>
+      <c r="L151" t="n">
+        <v>13</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
         <v>4</v>
       </c>
-      <c r="K151" t="n">
-        <v>6</v>
-      </c>
-      <c r="L151" t="n">
-        <v>10</v>
-      </c>
-      <c r="M151" t="n">
-        <v>1</v>
-      </c>
-      <c r="N151" t="n">
-        <v>2</v>
-      </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
@@ -72281,128 +72281,120 @@
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R151" t="n">
         <v>4</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T151" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U151" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V151" t="n">
+        <v>12</v>
+      </c>
+      <c r="W151" t="n">
         <v>11</v>
       </c>
-      <c r="W151" t="n">
-        <v>17</v>
-      </c>
       <c r="X151" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y151" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="Z151" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>Estadio Nemesio Díez</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>Avenida Constituyentes Poniente No. 1000, Colonia La Merced, Toluca de Lerdo</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA151" t="inlineStr"/>
+      <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="n">
         <v>1</v>
       </c>
       <c r="AD151" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE151" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AF151" t="n">
         <v>3.5</v>
       </c>
       <c r="AG151" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL151" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AN151" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AO151" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AR151" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="AS151" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AT151" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AU151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV151" t="n">
         <v>1</v>
       </c>
       <c r="AW151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY151" t="n">
         <v>0</v>
       </c>
       <c r="AZ151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB151" t="n">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="BC151" t="n">
         <v>1</v>
       </c>
       <c r="BD151" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="BE151" t="n">
         <v>0</v>
@@ -72417,73 +72409,73 @@
         <v>1</v>
       </c>
       <c r="BI151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ151" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BK151" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BL151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM151" t="n">
         <v>5</v>
       </c>
-      <c r="BM151" t="n">
-        <v>3</v>
-      </c>
       <c r="BN151" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BO151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS151" t="n">
         <v>2</v>
       </c>
       <c r="BT151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU151" t="n">
         <v>1</v>
       </c>
       <c r="BV151" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="BW151" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BX151" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="BY151" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="BZ151" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="CA151" t="n">
         <v>1.22</v>
       </c>
       <c r="CB151" t="n">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="CC151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD151" t="n">
         <v>0</v>
       </c>
       <c r="CE151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF151" t="n">
         <v>0</v>
@@ -72510,7 +72502,7 @@
         <v>0</v>
       </c>
       <c r="CN151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO151" t="n">
         <v>0</v>
@@ -72522,76 +72514,76 @@
         <v>1</v>
       </c>
       <c r="CR151" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="CS151" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="CT151" t="n">
         <v>1</v>
       </c>
       <c r="CU151" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CV151" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CW151" t="n">
         <v>1</v>
       </c>
       <c r="CX151" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CY151" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="CZ151" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="DA151" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="DB151" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC151" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD151" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DE151" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF151" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DG151" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DH151" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DI151" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DJ151" t="n">
         <v>47</v>
       </c>
-      <c r="DC151" t="n">
-        <v>78</v>
-      </c>
-      <c r="DD151" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE151" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="DF151" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DG151" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DH151" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DI151" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DJ151" t="n">
-        <v>35</v>
-      </c>
       <c r="DK151" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="DL151" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="DM151" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="DN151" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO151" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -72600,7 +72592,7 @@
         <v>1</v>
       </c>
       <c r="DR151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS151" t="b">
         <v>0</v>
@@ -72612,86 +72604,90 @@
         <v>0</v>
       </c>
       <c r="DV151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW151" t="n">
-        <v>18.03</v>
+        <v>30.73</v>
       </c>
       <c r="DX151" t="n">
-        <v>6.83</v>
+        <v>4.81</v>
       </c>
       <c r="DY151" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ151" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA151" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="EB151" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="EC151" t="inlineStr">
         <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="ED151" t="inlineStr"/>
-      <c r="EE151" t="inlineStr"/>
-      <c r="EF151" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EG151" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EH151" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="ED151" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EE151" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EF151" t="inlineStr"/>
+      <c r="EG151" t="inlineStr"/>
+      <c r="EH151" t="inlineStr"/>
       <c r="EI151" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EJ151" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EK151" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL151" t="inlineStr">
         <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EM151" t="inlineStr"/>
-      <c r="EN151" t="inlineStr"/>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EM151" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EN151" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
       <c r="EO151" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EP151" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.59</t>
         </is>
       </c>
     </row>
@@ -72711,162 +72707,170 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>León</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>América</t>
         </is>
       </c>
       <c r="F152" s="2" t="n">
         <v>45970.04166666666</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
+        <v>4</v>
+      </c>
+      <c r="K152" t="n">
         <v>6</v>
       </c>
-      <c r="K152" t="n">
-        <v>7</v>
-      </c>
       <c r="L152" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M152" t="n">
         <v>1</v>
       </c>
       <c r="N152" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
         <v>4</v>
-      </c>
-      <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>5</v>
       </c>
       <c r="R152" t="n">
         <v>4</v>
       </c>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T152" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U152" t="n">
+        <v>14</v>
+      </c>
+      <c r="V152" t="n">
         <v>11</v>
       </c>
-      <c r="V152" t="n">
-        <v>12</v>
-      </c>
       <c r="W152" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="X152" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y152" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="Z152" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA152" t="inlineStr"/>
-      <c r="AB152" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Díez</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>Avenida Constituyentes Poniente No. 1000, Colonia La Merced, Toluca de Lerdo</t>
+        </is>
+      </c>
       <c r="AC152" t="n">
         <v>1</v>
       </c>
       <c r="AD152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AF152" t="n">
         <v>3.5</v>
       </c>
       <c r="AG152" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AI152" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AJ152" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AK152" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AL152" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AM152" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AN152" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AO152" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AR152" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="AS152" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AT152" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AU152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV152" t="n">
         <v>1</v>
       </c>
       <c r="AW152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY152" t="n">
         <v>0</v>
       </c>
       <c r="AZ152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB152" t="n">
-        <v>1433</v>
+        <v>1424</v>
       </c>
       <c r="BC152" t="n">
         <v>1</v>
       </c>
       <c r="BD152" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="BE152" t="n">
         <v>0</v>
@@ -72881,73 +72885,73 @@
         <v>1</v>
       </c>
       <c r="BI152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL152" t="n">
         <v>5</v>
       </c>
-      <c r="BK152" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL152" t="n">
-        <v>2</v>
-      </c>
       <c r="BM152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN152" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BO152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS152" t="n">
         <v>2</v>
       </c>
       <c r="BT152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU152" t="n">
         <v>1</v>
       </c>
       <c r="BV152" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="BW152" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BX152" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="BY152" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="BZ152" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="CA152" t="n">
         <v>1.22</v>
       </c>
       <c r="CB152" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="CC152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD152" t="n">
         <v>0</v>
       </c>
       <c r="CE152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF152" t="n">
         <v>0</v>
@@ -72974,7 +72978,7 @@
         <v>0</v>
       </c>
       <c r="CN152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO152" t="n">
         <v>0</v>
@@ -72986,76 +72990,76 @@
         <v>1</v>
       </c>
       <c r="CR152" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="CS152" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CT152" t="n">
         <v>1</v>
       </c>
       <c r="CU152" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CV152" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CW152" t="n">
         <v>1</v>
       </c>
       <c r="CX152" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CY152" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="CZ152" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="DA152" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB152" t="n">
+        <v>47</v>
+      </c>
+      <c r="DC152" t="n">
         <v>78</v>
       </c>
-      <c r="DB152" t="n">
+      <c r="DD152" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DE152" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DF152" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DG152" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DH152" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DI152" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DJ152" t="n">
         <v>35</v>
       </c>
-      <c r="DC152" t="n">
-        <v>69</v>
-      </c>
-      <c r="DD152" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="DE152" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DF152" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="DG152" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DH152" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="DI152" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DJ152" t="n">
-        <v>47</v>
-      </c>
       <c r="DK152" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="DL152" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="DM152" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="DN152" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO152" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -73064,7 +73068,7 @@
         <v>1</v>
       </c>
       <c r="DR152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS152" t="b">
         <v>0</v>
@@ -73076,90 +73080,86 @@
         <v>0</v>
       </c>
       <c r="DV152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW152" t="n">
-        <v>30.73</v>
+        <v>18.03</v>
       </c>
       <c r="DX152" t="n">
-        <v>4.81</v>
+        <v>6.83</v>
       </c>
       <c r="DY152" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="DZ152" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="EA152" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EB152" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="EC152" t="inlineStr">
         <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="ED152" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EE152" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EF152" t="inlineStr"/>
-      <c r="EG152" t="inlineStr"/>
-      <c r="EH152" t="inlineStr"/>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="ED152" t="inlineStr"/>
+      <c r="EE152" t="inlineStr"/>
+      <c r="EF152" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EG152" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EH152" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
       <c r="EI152" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ152" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EK152" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EL152" t="inlineStr">
         <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EM152" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EN152" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EM152" t="inlineStr"/>
+      <c r="EN152" t="inlineStr"/>
       <c r="EO152" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EP152" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.39</t>
         </is>
       </c>
     </row>
@@ -75925,7 +75925,7 @@
         <v>1.29</v>
       </c>
       <c r="DE158" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF158" t="n">
         <v>1.37</v>
@@ -76901,7 +76901,7 @@
         <v>1.5</v>
       </c>
       <c r="DE160" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF160" t="n">
         <v>1.5</v>
@@ -78318,7 +78318,7 @@
         <v>84</v>
       </c>
       <c r="DD163" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE163" t="n">
         <v>1.29</v>
@@ -78798,7 +78798,7 @@
         <v>62</v>
       </c>
       <c r="DD164" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE164" t="n">
         <v>1.5</v>
@@ -79725,7 +79725,7 @@
         <v>1.95</v>
       </c>
       <c r="DE166" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DF166" t="n">
         <v>2.05</v>
@@ -80213,7 +80213,7 @@
         <v>1.76</v>
       </c>
       <c r="DE167" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF167" t="n">
         <v>1.79</v>
@@ -80682,7 +80682,7 @@
         <v>88</v>
       </c>
       <c r="DD168" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DE168" t="n">
         <v>1.76</v>
@@ -81162,7 +81162,7 @@
         <v>55</v>
       </c>
       <c r="DD169" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE169" t="n">
         <v>1.95</v>
@@ -81650,10 +81650,10 @@
         <v>69</v>
       </c>
       <c r="DD170" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DE170" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DF170" t="n">
         <v>1.95</v>
@@ -81683,7 +81683,7 @@
         <v>3.59</v>
       </c>
       <c r="DO170" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -81800,6 +81800,478 @@
       <c r="EP170" t="inlineStr">
         <is>
           <t>2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Mexico_Liga_MX_2025-2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>46006.04166666666</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="n">
+        <v>3</v>
+      </c>
+      <c r="J171" t="n">
+        <v>11</v>
+      </c>
+      <c r="K171" t="n">
+        <v>5</v>
+      </c>
+      <c r="L171" t="n">
+        <v>16</v>
+      </c>
+      <c r="M171" t="n">
+        <v>4</v>
+      </c>
+      <c r="N171" t="n">
+        <v>3</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>12</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2</v>
+      </c>
+      <c r="S171" t="n">
+        <v>19</v>
+      </c>
+      <c r="T171" t="n">
+        <v>5</v>
+      </c>
+      <c r="U171" t="n">
+        <v>31</v>
+      </c>
+      <c r="V171" t="n">
+        <v>7</v>
+      </c>
+      <c r="W171" t="n">
+        <v>17</v>
+      </c>
+      <c r="X171" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>Estadio Nemesio Díez</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>Avenida Constituyentes Poniente No. 1000, Colonia La Merced, Toluca de Lerdo</t>
+        </is>
+      </c>
+      <c r="AC171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>1424</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR171" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV171" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW171" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX171" t="n">
+        <v>142</v>
+      </c>
+      <c r="BY171" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CA171" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CB171" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="CC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP171" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR171" t="n">
+        <v>34</v>
+      </c>
+      <c r="CS171" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU171" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV171" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW171" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX171" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY171" t="n">
+        <v>18</v>
+      </c>
+      <c r="CZ171" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA171" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB171" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC171" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD171" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DE171" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DF171" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG171" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH171" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI171" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ171" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK171" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL171" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM171" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DN171" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="DO171" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU171" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV171" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW171" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="DX171" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="DY171" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="DZ171" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="EA171" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="EB171" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="EC171" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="ED171" t="inlineStr"/>
+      <c r="EE171" t="inlineStr"/>
+      <c r="EF171" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EG171" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH171" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EI171" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EJ171" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EK171" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EL171" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM171" t="inlineStr"/>
+      <c r="EN171" t="inlineStr"/>
+      <c r="EO171" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EP171" t="inlineStr">
+        <is>
+          <t>2.32</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -19112,7 +19112,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45885.96180555555</v>
+        <v>45885.96319444444</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -29072,7 +29072,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45900.04513888889</v>
+        <v>45900.04652777778</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -35256,7 +35256,7 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45918.04513888889</v>
+        <v>45918.04652777778</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -36695,41 +36695,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tijuana</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>León</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45920.125</v>
       </c>
       <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" t="n">
         <v>5</v>
       </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>5</v>
-      </c>
-      <c r="J76" t="n">
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
         <v>4</v>
       </c>
-      <c r="K76" t="n">
-        <v>3</v>
-      </c>
-      <c r="L76" t="n">
-        <v>7</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2</v>
-      </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
@@ -36737,128 +36737,120 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
         <v>3</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U76" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V76" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="W76" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="X76" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Y76" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Z76" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Estadio Caliente</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Boulevard Agua Caliente 12027, Colonia Hipódromo, Tijuana</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AF76" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AG76" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="AK76" t="n">
         <v>1.58</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AN76" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AS76" t="n">
-        <v>3.8</v>
+        <v>3.29</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AU76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW76" t="n">
         <v>0</v>
       </c>
       <c r="AX76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ76" t="n">
         <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB76" t="n">
-        <v>1418</v>
+        <v>-1</v>
       </c>
       <c r="BC76" t="n">
         <v>1</v>
       </c>
       <c r="BD76" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36873,76 +36865,76 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN76" t="n">
         <v>4</v>
       </c>
-      <c r="BJ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL76" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM76" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN76" t="n">
-        <v>2</v>
-      </c>
       <c r="BO76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU76" t="n">
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="BW76" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="BX76" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BY76" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="BZ76" t="n">
-        <v>1.99</v>
+        <v>1.54</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.78</v>
+        <v>1.23</v>
       </c>
       <c r="CB76" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
       </c>
       <c r="CD76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE76" t="n">
         <v>0</v>
       </c>
       <c r="CF76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG76" t="n">
         <v>0</v>
@@ -36963,7 +36955,7 @@
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN76" t="n">
         <v>0</v>
@@ -36978,73 +36970,73 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CS76" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="CV76" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY76" t="n">
         <v>7</v>
       </c>
-      <c r="CY76" t="n">
-        <v>12</v>
-      </c>
       <c r="CZ76" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="DA76" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="DB76" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="DC76" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.5</v>
+        <v>0.82</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="DF76" t="n">
-        <v>1.63</v>
+        <v>0.75</v>
       </c>
       <c r="DG76" t="n">
-        <v>1.38</v>
+        <v>0.75</v>
       </c>
       <c r="DH76" t="n">
-        <v>1.63</v>
+        <v>0.75</v>
       </c>
       <c r="DI76" t="n">
-        <v>1.38</v>
+        <v>0.75</v>
       </c>
       <c r="DJ76" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="DK76" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="DL76" t="n">
-        <v>1.19</v>
+        <v>0.99</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="DO76" t="n">
         <v>17</v>
@@ -37056,106 +37048,114 @@
         <v>1</v>
       </c>
       <c r="DR76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU76" t="b">
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>28.92</v>
+        <v>30.83</v>
       </c>
       <c r="DX76" t="n">
-        <v>4.12</v>
+        <v>4.26</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EI76" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EK76" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL76" t="inlineStr">
         <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="EM76" t="inlineStr"/>
-      <c r="EN76" t="inlineStr"/>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EM76" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EN76" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
       <c r="EO76" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EP76" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.43</t>
         </is>
       </c>
     </row>
@@ -37175,40 +37175,40 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mazatlán</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>León</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45920.125</v>
+        <v>45920.12847222222</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K77" t="n">
         <v>3</v>
       </c>
       <c r="L77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -37217,120 +37217,128 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R77" t="n">
         <v>3</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T77" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U77" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V77" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="W77" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="X77" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Y77" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z77" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Estadio Caliente</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Boulevard Agua Caliente 12027, Colonia Hipódromo, Tijuana</t>
+        </is>
+      </c>
       <c r="AC77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AF77" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AJ77" t="n">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="AK77" t="n">
         <v>1.58</v>
       </c>
       <c r="AL77" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AM77" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AN77" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="AO77" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AR77" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AS77" t="n">
-        <v>3.29</v>
+        <v>3.8</v>
       </c>
       <c r="AT77" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AU77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW77" t="n">
         <v>0</v>
       </c>
       <c r="AX77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ77" t="n">
         <v>2</v>
       </c>
       <c r="BA77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB77" t="n">
-        <v>-1</v>
+        <v>1418</v>
       </c>
       <c r="BC77" t="n">
         <v>1</v>
       </c>
       <c r="BD77" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="BE77" t="n">
         <v>0</v>
@@ -37345,76 +37353,76 @@
         <v>1</v>
       </c>
       <c r="BI77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ77" t="n">
         <v>1</v>
       </c>
       <c r="BK77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL77" t="n">
         <v>2</v>
       </c>
       <c r="BM77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BN77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU77" t="n">
         <v>1</v>
       </c>
       <c r="BV77" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="BW77" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="BX77" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY77" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="BZ77" t="n">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="CA77" t="n">
-        <v>1.23</v>
+        <v>0.78</v>
       </c>
       <c r="CB77" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CC77" t="n">
         <v>0</v>
       </c>
       <c r="CD77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE77" t="n">
         <v>0</v>
       </c>
       <c r="CF77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG77" t="n">
         <v>0</v>
@@ -37435,7 +37443,7 @@
         <v>0</v>
       </c>
       <c r="CM77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
@@ -37450,73 +37458,73 @@
         <v>1</v>
       </c>
       <c r="CR77" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CS77" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY77" t="n">
         <v>12</v>
       </c>
-      <c r="CT77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU77" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV77" t="n">
-        <v>20</v>
-      </c>
-      <c r="CW77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX77" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY77" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ77" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="DA77" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="DB77" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="DC77" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="DD77" t="n">
-        <v>0.82</v>
+        <v>1.5</v>
       </c>
       <c r="DE77" t="n">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="DF77" t="n">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="DG77" t="n">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="DH77" t="n">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="DI77" t="n">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="DJ77" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="DK77" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="DL77" t="n">
-        <v>0.99</v>
+        <v>1.19</v>
       </c>
       <c r="DM77" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="DN77" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="DO77" t="n">
         <v>17</v>
@@ -37528,114 +37536,106 @@
         <v>1</v>
       </c>
       <c r="DR77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU77" t="b">
         <v>0</v>
       </c>
       <c r="DV77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW77" t="n">
-        <v>30.83</v>
+        <v>28.92</v>
       </c>
       <c r="DX77" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EG77" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EH77" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EI77" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL77" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="EM77" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EN77" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr"/>
+      <c r="EN77" t="inlineStr"/>
       <c r="EO77" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EP77" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -44816,7 +44816,7 @@
         <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -44868,7 +44868,7 @@
         <v>3</v>
       </c>
       <c r="AD93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE93" t="n">
         <v>1.5</v>
@@ -44982,7 +44982,7 @@
         <v>2</v>
       </c>
       <c r="BP93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ93" t="n">
         <v>1</v>
@@ -44991,7 +44991,7 @@
         <v>1</v>
       </c>
       <c r="BS93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT93" t="n">
         <v>2</v>
@@ -51896,7 +51896,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45936.04166666666</v>
+        <v>45936.06597222222</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -52897,7 +52897,7 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R110" t="n">
         <v>4</v>
@@ -52909,7 +52909,7 @@
         <v>9</v>
       </c>
       <c r="U110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V110" t="n">
         <v>13</v>
@@ -53084,13 +53084,13 @@
         <v>63</v>
       </c>
       <c r="BZ110" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="CA110" t="n">
         <v>1.27</v>
       </c>
       <c r="CB110" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="CC110" t="n">
         <v>0</v>
@@ -53393,10 +53393,10 @@
         <v>5</v>
       </c>
       <c r="Y111" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z111" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         <v>10</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N112" t="n">
         <v>5</v>
@@ -53865,7 +53865,7 @@
         </is>
       </c>
       <c r="AC112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD112" t="n">
         <v>5</v>
@@ -53985,7 +53985,7 @@
         <v>1</v>
       </c>
       <c r="BQ112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR112" t="n">
         <v>4</v>
@@ -53994,7 +53994,7 @@
         <v>1</v>
       </c>
       <c r="BT112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU112" t="n">
         <v>1</v>
@@ -54777,10 +54777,10 @@
         <v>17</v>
       </c>
       <c r="Y114" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z114" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
@@ -55265,10 +55265,10 @@
         <v>10</v>
       </c>
       <c r="Y115" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z115" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
@@ -55703,13 +55703,13 @@
         <v>2</v>
       </c>
       <c r="S116" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T116" t="n">
         <v>12</v>
       </c>
       <c r="U116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V116" t="n">
         <v>14</v>
@@ -55721,10 +55721,10 @@
         <v>14</v>
       </c>
       <c r="Y116" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z116" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
@@ -55884,13 +55884,13 @@
         <v>36</v>
       </c>
       <c r="BZ116" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="CA116" t="n">
         <v>1.31</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="CC116" t="n">
         <v>1</v>
@@ -55959,7 +55959,7 @@
         <v>6</v>
       </c>
       <c r="CY116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CZ116" t="n">
         <v>63</v>
@@ -56673,10 +56673,10 @@
         <v>11</v>
       </c>
       <c r="Y118" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z118" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
@@ -57409,10 +57409,10 @@
         <v>1.74</v>
       </c>
       <c r="DM119" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DN119" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DO119" t="n">
         <v>17</v>
@@ -61383,10 +61383,10 @@
         <v>17</v>
       </c>
       <c r="W128" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="X128" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y128" t="n">
         <v>49</v>
@@ -61669,10 +61669,10 @@
         <v>1.26</v>
       </c>
       <c r="DM128" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DN128" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DO128" t="n">
         <v>17</v>
@@ -64033,10 +64033,10 @@
         <v>1.91</v>
       </c>
       <c r="DM133" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DN133" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="DO133" t="n">
         <v>21</v>
@@ -64200,7 +64200,7 @@
         <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -64252,7 +64252,7 @@
         <v>2</v>
       </c>
       <c r="AD134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE134" t="n">
         <v>2.05</v>
@@ -64372,13 +64372,13 @@
         <v>1</v>
       </c>
       <c r="BR134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS134" t="n">
         <v>5</v>
       </c>
       <c r="BT134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU134" t="n">
         <v>1</v>
@@ -65903,7 +65903,7 @@
         <v>6</v>
       </c>
       <c r="CY137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ137" t="n">
         <v>57</v>
@@ -66093,10 +66093,10 @@
         <v>12</v>
       </c>
       <c r="M138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>1</v>
@@ -66145,10 +66145,10 @@
         </is>
       </c>
       <c r="AC138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE138" t="n">
         <v>2.3</v>
@@ -66265,16 +66265,16 @@
         <v>0</v>
       </c>
       <c r="BQ138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS138" t="n">
         <v>0</v>
       </c>
       <c r="BT138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU138" t="n">
         <v>1</v>
@@ -66602,13 +66602,13 @@
         <v>4</v>
       </c>
       <c r="T139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U139" t="n">
         <v>8</v>
       </c>
       <c r="V139" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W139" t="n">
         <v>11</v>
@@ -66783,10 +66783,10 @@
         <v>1.1</v>
       </c>
       <c r="CA139" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="CB139" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="CC139" t="n">
         <v>0</v>
@@ -66894,13 +66894,13 @@
         <v>20</v>
       </c>
       <c r="DL139" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DM139" t="n">
         <v>1.93</v>
       </c>
       <c r="DN139" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DO139" t="n">
         <v>17</v>
@@ -67309,7 +67309,7 @@
         <v>19</v>
       </c>
       <c r="CS140" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT140" t="n">
         <v>1</v>
@@ -67318,7 +67318,7 @@
         <v>11</v>
       </c>
       <c r="CV140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CW140" t="n">
         <v>1</v>
@@ -67846,13 +67846,13 @@
         <v>24</v>
       </c>
       <c r="DL141" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DM141" t="n">
         <v>1.89</v>
       </c>
       <c r="DN141" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="DO141" t="n">
         <v>21</v>
@@ -69210,7 +69210,7 @@
         <v>1</v>
       </c>
       <c r="CR144" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CS144" t="n">
         <v>16</v>
@@ -70647,7 +70647,7 @@
         <v>7</v>
       </c>
       <c r="CY147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ147" t="n">
         <v>57</v>
@@ -70856,7 +70856,7 @@
         <v>5</v>
       </c>
       <c r="N148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O148" t="n">
         <v>1</v>
@@ -70868,13 +70868,13 @@
         <v>2</v>
       </c>
       <c r="R148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S148" t="n">
         <v>3</v>
       </c>
       <c r="T148" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U148" t="n">
         <v>5</v>
@@ -70889,10 +70889,10 @@
         <v>16</v>
       </c>
       <c r="Y148" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z148" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="inlineStr"/>
@@ -70900,7 +70900,7 @@
         <v>7</v>
       </c>
       <c r="AD148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE148" t="n">
         <v>3.15</v>
@@ -71020,13 +71020,13 @@
         <v>3</v>
       </c>
       <c r="BR148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS148" t="n">
         <v>4</v>
       </c>
       <c r="BT148" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU148" t="n">
         <v>1</v>
@@ -71047,10 +71047,10 @@
         <v>0.68</v>
       </c>
       <c r="CA148" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="CB148" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="CC148" t="n">
         <v>1</v>
@@ -71345,10 +71345,10 @@
         <v>8</v>
       </c>
       <c r="Y149" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z149" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
@@ -71562,10 +71562,10 @@
         <v>1</v>
       </c>
       <c r="CR149" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CS149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CT149" t="n">
         <v>1</v>
@@ -72097,10 +72097,10 @@
         <v>1.53</v>
       </c>
       <c r="DM150" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DN150" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DO150" t="n">
         <v>19</v>
@@ -72305,10 +72305,10 @@
         <v>13</v>
       </c>
       <c r="Y151" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z151" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr"/>
@@ -72577,10 +72577,10 @@
         <v>1.25</v>
       </c>
       <c r="DM151" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DN151" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="DO151" t="n">
         <v>17</v>
@@ -72993,7 +72993,7 @@
         <v>24</v>
       </c>
       <c r="CS152" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CT152" t="n">
         <v>1</v>
@@ -73230,13 +73230,13 @@
         <v>11</v>
       </c>
       <c r="T153" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U153" t="n">
         <v>16</v>
       </c>
       <c r="V153" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W153" t="n">
         <v>7</v>
@@ -73245,10 +73245,10 @@
         <v>17</v>
       </c>
       <c r="Y153" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z153" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
@@ -73411,10 +73411,10 @@
         <v>1.58</v>
       </c>
       <c r="CA153" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="CB153" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="CC153" t="n">
         <v>0</v>
@@ -73465,7 +73465,7 @@
         <v>20</v>
       </c>
       <c r="CS153" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CT153" t="n">
         <v>1</v>
@@ -74187,13 +74187,13 @@
         <v>5</v>
       </c>
       <c r="S155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T155" t="n">
         <v>8</v>
       </c>
       <c r="U155" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V155" t="n">
         <v>13</v>
@@ -74368,13 +74368,13 @@
         <v>95</v>
       </c>
       <c r="BZ155" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="CA155" t="n">
         <v>1.58</v>
       </c>
       <c r="CB155" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="CC155" t="n">
         <v>0</v>
@@ -74693,10 +74693,10 @@
         <v>21</v>
       </c>
       <c r="Y156" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z156" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
@@ -75461,10 +75461,10 @@
         <v>1.32</v>
       </c>
       <c r="DM157" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DN157" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DO157" t="n">
         <v>19</v>
@@ -75599,7 +75599,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -76087,7 +76087,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -76434,13 +76434,13 @@
         <v>15</v>
       </c>
       <c r="DL159" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DM159" t="n">
         <v>1.8</v>
       </c>
       <c r="DN159" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DO159" t="n">
         <v>19</v>
@@ -76575,7 +76575,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -78512,7 +78512,7 @@
         <v>4</v>
       </c>
       <c r="N164" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -78564,7 +78564,7 @@
         <v>4</v>
       </c>
       <c r="AD164" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE164" t="n">
         <v>1.3</v>
@@ -78684,13 +78684,13 @@
         <v>3</v>
       </c>
       <c r="BR164" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BS164" t="n">
         <v>3</v>
       </c>
       <c r="BT164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BU164" t="n">
         <v>1</v>
@@ -79746,13 +79746,13 @@
         <v>21</v>
       </c>
       <c r="DL166" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DM166" t="n">
         <v>1.92</v>
       </c>
       <c r="DN166" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="DO166" t="n">
         <v>21</v>
@@ -81189,10 +81189,10 @@
         <v>1.86</v>
       </c>
       <c r="DM169" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DN169" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="DO169" t="n">
         <v>21</v>
@@ -81626,7 +81626,7 @@
         <v>15</v>
       </c>
       <c r="CV170" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CW170" t="n">
         <v>1</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -90861,10 +90861,10 @@
         <v>4</v>
       </c>
       <c r="Y190" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z190" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AA190" t="inlineStr"/>
       <c r="AB190" t="inlineStr"/>
@@ -91323,13 +91323,13 @@
         <v>3</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T191" t="n">
         <v>10</v>
       </c>
       <c r="U191" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V191" t="n">
         <v>13</v>
@@ -91444,7 +91444,7 @@
         <v>0</v>
       </c>
       <c r="BF191" t="n">
-        <v>-1</v>
+        <v>17557</v>
       </c>
       <c r="BG191" t="n">
         <v>2</v>
@@ -91504,13 +91504,13 @@
         <v>72</v>
       </c>
       <c r="BZ191" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="CA191" t="n">
         <v>1.16</v>
       </c>
       <c r="CB191" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="CC191" t="n">
         <v>0</v>
@@ -91908,7 +91908,7 @@
         <v>0</v>
       </c>
       <c r="BF192" t="n">
-        <v>-1</v>
+        <v>34839</v>
       </c>
       <c r="BG192" t="n">
         <v>2</v>
@@ -92262,13 +92262,13 @@
         <v>5</v>
       </c>
       <c r="T193" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U193" t="n">
         <v>7</v>
       </c>
       <c r="V193" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W193" t="n">
         <v>16</v>
@@ -92443,10 +92443,10 @@
         <v>0.82</v>
       </c>
       <c r="CA193" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="CB193" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="CC193" t="n">
         <v>0</v>
@@ -92747,13 +92747,13 @@
         <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T194" t="n">
         <v>5</v>
       </c>
       <c r="U194" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V194" t="n">
         <v>5</v>
@@ -92928,13 +92928,13 @@
         <v>49</v>
       </c>
       <c r="BZ194" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="CA194" t="n">
         <v>0.44</v>
       </c>
       <c r="CB194" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="CC194" t="n">
         <v>0</v>
@@ -93812,7 +93812,7 @@
         <v>0</v>
       </c>
       <c r="BF196" t="n">
-        <v>-1</v>
+        <v>21487</v>
       </c>
       <c r="BG196" t="n">
         <v>2</v>
@@ -94176,13 +94176,13 @@
         <v>6</v>
       </c>
       <c r="R197" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S197" t="n">
         <v>15</v>
       </c>
       <c r="T197" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U197" t="n">
         <v>21</v>
@@ -94300,7 +94300,7 @@
         <v>0</v>
       </c>
       <c r="BF197" t="n">
-        <v>-1</v>
+        <v>11767</v>
       </c>
       <c r="BG197" t="n">
         <v>2</v>
@@ -94363,10 +94363,10 @@
         <v>1.9</v>
       </c>
       <c r="CA197" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="CB197" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="CC197" t="n">
         <v>0</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -91950,13 +91950,13 @@
         <v>3</v>
       </c>
       <c r="T199" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U199" t="n">
         <v>4</v>
       </c>
       <c r="V199" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W199" t="n">
         <v>10</v>
@@ -92131,10 +92131,10 @@
         <v>0.46</v>
       </c>
       <c r="CA199" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="CB199" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="CC199" t="n">
         <v>0</v>
@@ -92421,10 +92421,10 @@
         <v>9</v>
       </c>
       <c r="Y200" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z200" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
@@ -92851,13 +92851,13 @@
         <v>7</v>
       </c>
       <c r="S201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T201" t="n">
         <v>10</v>
       </c>
       <c r="U201" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V201" t="n">
         <v>17</v>
@@ -93032,13 +93032,13 @@
         <v>83</v>
       </c>
       <c r="BZ201" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="CA201" t="n">
         <v>1.72</v>
       </c>
       <c r="CB201" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="CC201" t="n">
         <v>1</v>
@@ -93747,10 +93747,10 @@
         <v>4</v>
       </c>
       <c r="K203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L203" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M203" t="n">
         <v>1</v>
@@ -93768,25 +93768,25 @@
         <v>6</v>
       </c>
       <c r="R203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T203" t="n">
         <v>7</v>
       </c>
       <c r="U203" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V203" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W203" t="n">
         <v>18</v>
       </c>
       <c r="X203" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y203" t="n">
         <v>56</v>
@@ -93952,13 +93952,13 @@
         <v>79</v>
       </c>
       <c r="BZ203" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="CA203" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="CB203" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="CC203" t="n">
         <v>0</v>
@@ -94006,16 +94006,16 @@
         <v>1</v>
       </c>
       <c r="CR203" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CS203" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CT203" t="n">
         <v>1</v>
       </c>
       <c r="CU203" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CV203" t="n">
         <v>18</v>
@@ -94027,7 +94027,7 @@
         <v>8</v>
       </c>
       <c r="CY203" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ203" t="n">
         <v>58</v>
@@ -95540,13 +95540,13 @@
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K207" t="n">
         <v>3</v>
       </c>
       <c r="L207" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M207" t="n">
         <v>1</v>
@@ -95691,28 +95691,28 @@
         <v>-1</v>
       </c>
       <c r="BG207" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH207" t="n">
         <v>1</v>
       </c>
       <c r="BI207" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BJ207" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK207" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL207" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM207" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BN207" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO207" t="n">
         <v>0</v>
@@ -95787,10 +95787,10 @@
         <v>0</v>
       </c>
       <c r="CM207" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN207" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO207" t="n">
         <v>0</v>
@@ -95802,7 +95802,7 @@
         <v>1</v>
       </c>
       <c r="CR207" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CS207" t="n">
         <v>16</v>
@@ -95901,16 +95901,24 @@
       </c>
       <c r="DX207" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="DY207" t="inlineStr">
         <is>
-          <t>3.23</t>
-        </is>
-      </c>
-      <c r="DZ207" t="inlineStr"/>
-      <c r="EA207" t="inlineStr"/>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="DZ207" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EA207" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
       <c r="EB207" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -95928,26 +95936,34 @@
       </c>
       <c r="EE207" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EF207" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EG207" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EH207" t="inlineStr">
         <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EI207" t="inlineStr"/>
-      <c r="EJ207" t="inlineStr"/>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EI207" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EJ207" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
       <c r="EK207" t="inlineStr">
         <is>
           <t>1.56</t>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -93892,7 +93892,7 @@
         <v>0</v>
       </c>
       <c r="BF203" t="n">
-        <v>-1</v>
+        <v>19723</v>
       </c>
       <c r="BG203" t="n">
         <v>-1</v>
@@ -95127,13 +95127,13 @@
         <v>6</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T206" t="n">
         <v>10</v>
       </c>
       <c r="U206" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V206" t="n">
         <v>16</v>
@@ -95145,10 +95145,10 @@
         <v>7</v>
       </c>
       <c r="Y206" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z206" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA206" t="inlineStr"/>
       <c r="AB206" t="inlineStr"/>
@@ -95300,13 +95300,13 @@
         <v>94</v>
       </c>
       <c r="BZ206" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="CA206" t="n">
         <v>1.74</v>
       </c>
       <c r="CB206" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="CC206" t="n">
         <v>0</v>
@@ -95688,7 +95688,7 @@
         <v>0</v>
       </c>
       <c r="BF207" t="n">
-        <v>-1</v>
+        <v>12338</v>
       </c>
       <c r="BG207" t="n">
         <v>2</v>
@@ -95802,7 +95802,7 @@
         <v>1</v>
       </c>
       <c r="CR207" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CS207" t="n">
         <v>16</v>
@@ -95823,7 +95823,7 @@
         <v>15</v>
       </c>
       <c r="CY207" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CZ207" t="n">
         <v>53</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -96042,13 +96042,13 @@
         <v>5</v>
       </c>
       <c r="T208" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U208" t="n">
         <v>10</v>
       </c>
       <c r="V208" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W208" t="n">
         <v>14</v>
@@ -96223,10 +96223,10 @@
         <v>1.18</v>
       </c>
       <c r="CA208" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="CB208" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="CC208" t="n">
         <v>0</v>
@@ -97832,13 +97832,13 @@
         <v>6</v>
       </c>
       <c r="R212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S212" t="n">
         <v>9</v>
       </c>
       <c r="T212" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U212" t="n">
         <v>15</v>
@@ -98019,10 +98019,10 @@
         <v>1.51</v>
       </c>
       <c r="CA212" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="CB212" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="CC212" t="n">
         <v>0</v>
@@ -98724,7 +98724,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>46061.04166666666</v>
+        <v>46061.04513888889</v>
       </c>
       <c r="G214" t="n">
         <v>2</v>
@@ -99196,7 +99196,7 @@
         </is>
       </c>
       <c r="F215" s="2" t="n">
-        <v>46061.04166666666</v>
+        <v>46061.04583333333</v>
       </c>
       <c r="G215" t="n">
         <v>2</v>
@@ -99652,7 +99652,7 @@
         </is>
       </c>
       <c r="F216" s="2" t="n">
-        <v>46061.125</v>
+        <v>46061.13194444445</v>
       </c>
       <c r="G216" t="n">
         <v>1</v>
@@ -99691,13 +99691,13 @@
         <v>2</v>
       </c>
       <c r="S216" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T216" t="n">
         <v>2</v>
       </c>
       <c r="U216" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V216" t="n">
         <v>4</v>
@@ -99872,13 +99872,13 @@
         <v>96</v>
       </c>
       <c r="BZ216" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="CA216" t="n">
         <v>0.58</v>
       </c>
       <c r="CB216" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="CC216" t="n">
         <v>0</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -98310,13 +98310,13 @@
         <v>9</v>
       </c>
       <c r="T213" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U213" t="n">
         <v>14</v>
       </c>
       <c r="V213" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W213" t="n">
         <v>9</v>
@@ -98325,10 +98325,10 @@
         <v>5</v>
       </c>
       <c r="Y213" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z213" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
@@ -98491,10 +98491,10 @@
         <v>1.34</v>
       </c>
       <c r="CA213" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="CB213" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="CC213" t="n">
         <v>0</v>
@@ -99229,13 +99229,13 @@
         <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R215" t="n">
         <v>3</v>
       </c>
       <c r="S215" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T215" t="n">
         <v>9</v>
@@ -99416,13 +99416,13 @@
         <v>84</v>
       </c>
       <c r="BZ215" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="CA215" t="n">
         <v>1.24</v>
       </c>
       <c r="CB215" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="CC215" t="n">
         <v>0</v>

--- a/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
+++ b/data/matches/leagues/Mexico_Liga_MX_2025-2026.xlsx
@@ -101979,13 +101979,13 @@
         <v>2</v>
       </c>
       <c r="S221" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T221" t="n">
         <v>7</v>
       </c>
       <c r="U221" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V221" t="n">
         <v>9</v>
@@ -102160,13 +102160,13 @@
         <v>79</v>
       </c>
       <c r="BZ221" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="CA221" t="n">
         <v>0.88</v>
       </c>
       <c r="CB221" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="CC221" t="n">
         <v>0</v>
@@ -102223,7 +102223,7 @@
         <v>1</v>
       </c>
       <c r="CU221" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CV221" t="n">
         <v>17</v>
@@ -103341,10 +103341,10 @@
         <v>8</v>
       </c>
       <c r="Y224" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z224" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
@@ -103798,13 +103798,13 @@
         <v>14</v>
       </c>
       <c r="T225" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U225" t="n">
         <v>17</v>
       </c>
       <c r="V225" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W225" t="n">
         <v>8</v>
@@ -103813,10 +103813,10 @@
         <v>15</v>
       </c>
       <c r="Y225" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z225" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
@@ -103979,10 +103979,10 @@
         <v>1.37</v>
       </c>
       <c r="CA225" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="CB225" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="CC225" t="n">
         <v>1</v>
@@ -104030,10 +104030,10 @@
         <v>1</v>
       </c>
       <c r="CR225" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CS225" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT225" t="n">
         <v>1</v>
